--- a/regions/LME_032/models/32_1_Arabian_Sea_off_Karnataka_(2000)/sppr_source.xlsx
+++ b/regions/LME_032/models/32_1_Arabian_Sea_off_Karnataka_(2000)/sppr_source.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="groups_df" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="sppr_PP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="sppr_inner" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="model_health" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="footprint" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="mc_diagnostics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="run_notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="groups_df" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sppr_PP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sppr_inner" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_health" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="footprint" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mc_diagnostics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="run_notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,6 +617,7 @@
           <t>Import</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -639,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -836,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-1.704653490138298</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>0</v>
@@ -924,7 +925,7 @@
         <v>1800</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.2933959225165381</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>0</v>
@@ -1012,7 +1013,7 @@
         <v>580</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.2248639561689174</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>0</v>
@@ -1100,7 +1101,7 @@
         <v>64</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.02622173693601582</v>
+        <v>0</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>0</v>
@@ -1188,7 +1189,7 @@
         <v>390</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.07788884941764707</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>0</v>
@@ -1276,7 +1277,7 @@
         <v>266</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.2217007724403448</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>0</v>
@@ -1364,7 +1365,7 @@
         <v>8.864308000000001</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.0002140727238826301</v>
+        <v>0</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>0</v>
@@ -1452,7 +1453,7 @@
         <v>7.16968</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-0.004381676932298184</v>
+        <v>0</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>0</v>
@@ -1540,7 +1541,7 @@
         <v>0.7259</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0.002236583453453567</v>
+        <v>0</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>0</v>
@@ -1628,7 +1629,7 @@
         <v>32.75388</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.006694370471310052</v>
+        <v>0</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>0</v>
@@ -1716,7 +1717,7 @@
         <v>6.942646999999999</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>-0.003621997038152247</v>
+        <v>0</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>0</v>
@@ -1804,7 +1805,7 @@
         <v>10.868352</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0.004494960000000048</v>
+        <v>0</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>0</v>
@@ -1892,7 +1893,7 @@
         <v>3.262129000000001</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>-0.001912184636008618</v>
+        <v>0</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1981,7 @@
         <v>9.30044</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>0.001285952321492534</v>
+        <v>0</v>
       </c>
       <c r="U17" s="2" t="n">
         <v>0</v>
@@ -2068,7 +2069,7 @@
         <v>0.8919720000000002</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>-0.005279694129610213</v>
+        <v>0</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>0</v>
@@ -2156,7 +2157,7 @@
         <v>2.55282</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.003849941501501419</v>
+        <v>0</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>0</v>
@@ -2244,7 +2245,7 @@
         <v>0.7232379999999998</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>0.001233559705289683</v>
+        <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>0</v>
@@ -2332,7 +2333,7 @@
         <v>5.747742000000001</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>-0.001814448581958783</v>
+        <v>0</v>
       </c>
       <c r="U21" s="2" t="n">
         <v>0</v>
@@ -2420,7 +2421,7 @@
         <v>0.256128</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>0.0001098879999999886</v>
+        <v>0</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>0</v>
@@ -2508,7 +2509,7 @@
         <v>0.249612</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>-0.0007748651948051993</v>
+        <v>0</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>0</v>
@@ -2596,7 +2597,7 @@
         <v>0.08839599999999999</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>0.0008835000000000006</v>
+        <v>0</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>0</v>
@@ -2684,7 +2685,7 @@
         <v>0.04582500000000001</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>0.0001856749999999963</v>
+        <v>0</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>0</v>
@@ -2772,7 +2773,7 @@
         <v>0.19</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>0.0001938</v>
+        <v>0</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>0</v>
@@ -2829,6 +2830,8 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2859,97 +2862,97 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Ulanowicz_globalTEmean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ulanowicz_TE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EwE_TE_noEE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>EwE_TE_EE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>SPPR_2015</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>new_TE_noEEfix</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>new_TE_EEfix</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>new_GE</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>new_WithEgestion</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>sym_TE_asPP</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sym_TE_asDC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>sym_GE_asPP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>sym_GE_asDC</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sym_WithEgestion_asPP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>sym_WithEgestion_asDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MC_new_GE</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>SPPR_1995_TEmean_catch</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -2962,9 +2965,10 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
@@ -2992,19 +2996,25 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3017,9 +3027,10 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
@@ -3030,14 +3041,14 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0.3223803903634934</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
       </c>
@@ -3068,7 +3079,10 @@
       <c r="V3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
+      <c r="W3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3081,24 +3095,25 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.842</v>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
@@ -3132,7 +3147,10 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="X4" t="n">
+      <c r="W4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3145,59 +3163,63 @@
           <t>Micro Zooplankton</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" s="2" t="n">
         <v>6.223128848904347</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>5.102040816326531</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>5.102040816326531</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5.102040816326531</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>5.102040816326531</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>5.102040816326531</v>
       </c>
       <c r="M5" s="2" t="n">
+        <v>5.102040816326531</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>5.102040816326531</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>5.10204081632653</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>5.10204081632653</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="V5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>5.036055358031964</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>5.124599030923125</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.881896884283592</v>
+      <c r="W5" s="2" t="n">
+        <v>5.027068645578732</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>5.123573062782874</v>
       </c>
     </row>
     <row r="6">
@@ -3209,59 +3231,63 @@
           <t>Large zooplankton</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" s="2" t="n">
         <v>25.20558388046248</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
+        <v>15.94929274210823</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>21.82880466472303</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>22.27429047420718</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>21.44571428571428</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>14.15314285714286</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>22.2742904742072</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>22.2742904742072</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>21.4457142857143</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="T6" s="2" t="n">
         <v>21.4457142857143</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="U6" s="2" t="n">
         <v>14.1531428571429</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="V6" s="2" t="n">
         <v>14.1531428571429</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>21.7943514061429</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>22.32385000367074</v>
-      </c>
-      <c r="X6" t="n">
-        <v>15.94929274210823</v>
+      <c r="W6" s="2" t="n">
+        <v>21.44097580734458</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>22.18757739942376</v>
       </c>
     </row>
     <row r="7">
@@ -3273,59 +3299,63 @@
           <t>Micro Nekton</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" s="2" t="n">
         <v>103.5813817095471</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
+        <v>52.8465198923722</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>117.3357669362273</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>117.3357669362273</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>91.28722667638483</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>131.1429729548547</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>131.0186245803873</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>131.0186245803873</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="O7" s="2" t="n">
         <v>95.85088435374149</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>50.91469518716576</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>131.018624580387</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>131.018624580387</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>95.85088435374151</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>95.85088435374151</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>50.9146951871658</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="V7" s="2" t="n">
         <v>50.9146951871658</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>99.70840479436427</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>135.1944639731009</v>
-      </c>
-      <c r="X7" t="n">
-        <v>52.8465198923722</v>
+      <c r="W7" s="2" t="n">
+        <v>95.83489499230244</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>132.8012361730654</v>
       </c>
     </row>
     <row r="8">
@@ -3337,59 +3367,63 @@
           <t>Meiobenthos</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" s="2" t="n">
         <v>0.08367779418903544</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
+        <v>0.05254773126183929</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>0.09612080757235872</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>0.0961208075723587</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>0.03585306122448979</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>3.409782525859228</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>0.1172434964829621</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>0.1172434964829621</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>0.03773584905660377</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>0.02434900236726412</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>0.117243496482962</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>0.117243496482962</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>0.0377358490566038</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="T8" s="2" t="n">
         <v>0.0377358490566038</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="U8" s="2" t="n">
         <v>0.0243490023672641</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="V8" s="2" t="n">
         <v>0.0243490023672641</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>0.03848897627554826</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>0.119552806205362</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.05254773126183929</v>
+      <c r="W8" s="2" t="n">
+        <v>0.0386526355663186</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0.1205904963532257</v>
       </c>
     </row>
     <row r="9">
@@ -3401,59 +3435,63 @@
           <t>Heterotrophic Benthos</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" s="2" t="n">
         <v>13.13335276301223</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
+        <v>6.891211836915105</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>62.62495666609252</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>62.62495666609252</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>7.765494626595472</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>260.72059691995</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>191.6577120591832</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>191.6577120591832</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>8.155035093417276</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>4.45494731670138</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>191.657712059183</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>191.657712059183</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>8.155035093417281</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>8.155035093417281</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>4.45494731670138</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="V9" s="2" t="n">
         <v>4.45494731670138</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>8.253363721634036</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>210.6771933229766</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6.891211836915105</v>
+      <c r="W9" s="2" t="n">
+        <v>8.150526838045792</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>205.2990360859135</v>
       </c>
     </row>
     <row r="10">
@@ -3465,59 +3503,63 @@
           <t>Benthic Omnivores</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" s="2" t="n">
         <v>23.42316035580676</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
+        <v>10.30716214090233</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>58.86643558878648</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>58.86643558878647</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>57.68910687701074</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>234.3262107631635</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>170.6617579129059</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>170.6617579129059</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>11.23293113566132</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>5.328794768680671</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>170.661757912906</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="R10" s="2" t="n">
         <v>170.661757912906</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="S10" s="2" t="n">
         <v>11.2329311356613</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="T10" s="2" t="n">
         <v>11.2329311356613</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="U10" s="2" t="n">
         <v>5.32879476868067</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="V10" s="2" t="n">
         <v>5.32879476868067</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>11.15929512194512</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>191.0637789111209</v>
-      </c>
-      <c r="X10" t="n">
-        <v>10.30716214090233</v>
+      <c r="W10" s="2" t="n">
+        <v>11.34832419866604</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>184.4418734846431</v>
       </c>
     </row>
     <row r="11">
@@ -3529,59 +3571,63 @@
           <t>Shrimps</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" s="2" t="n">
         <v>90.21080501805984</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
+        <v>43.82355419599745</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>40.50231375945157</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>40.50231375945157</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>39.69226748426254</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>49.86108608645311</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>45.65511001550941</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>45.65511001550941</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>35.65817966136099</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="P11" s="2" t="n">
         <v>18.39547065938578</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>45.6551100155094</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="R11" s="2" t="n">
         <v>45.6551100155094</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="S11" s="2" t="n">
         <v>35.658179661361</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="T11" s="2" t="n">
         <v>35.658179661361</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="U11" s="2" t="n">
         <v>18.3954706593858</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="V11" s="2" t="n">
         <v>18.3954706593858</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>36.88091280633074</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>47.24459970241958</v>
-      </c>
-      <c r="X11" t="n">
-        <v>43.82355419599745</v>
+      <c r="W11" s="2" t="n">
+        <v>35.70633926104802</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>46.49961816616637</v>
       </c>
     </row>
     <row r="12">
@@ -3593,59 +3639,63 @@
           <t>Crabs &amp; Lobster</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" s="2" t="n">
         <v>56.11716397410842</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
+        <v>20.91214152184571</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>45.04131904158248</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>45.04131904158247</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>43.96032738458449</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>117.553731679799</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="M12" s="2" t="n">
         <v>89.64171006771271</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="N12" s="2" t="n">
         <v>89.64171006771271</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="O12" s="2" t="n">
         <v>23.09254983758252</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>9.115855991521704</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>89.64171006771269</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="R12" s="2" t="n">
         <v>89.64171006771269</v>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="S12" s="2" t="n">
         <v>23.0925498375825</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="T12" s="2" t="n">
         <v>23.0925498375825</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="U12" s="2" t="n">
         <v>9.1158559915217</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="V12" s="2" t="n">
         <v>9.1158559915217</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>24.07143085842931</v>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>98.84681219182602</v>
-      </c>
-      <c r="X12" t="n">
-        <v>20.91214152184571</v>
+      <c r="W12" s="2" t="n">
+        <v>23.5712987176275</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>94.33421138508965</v>
       </c>
     </row>
     <row r="13">
@@ -3657,59 +3707,63 @@
           <t>Anchovies</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" s="2" t="n">
         <v>185.3606009254594</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
+        <v>85.29867757995484</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>283.8477380659185</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>283.8477380659184</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>277.3192400904023</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>324.4406618972106</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>315.3512792915741</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>315.3512792915741</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>241.7646634587855</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>117.5090403112203</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>315.351279291574</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="R13" s="2" t="n">
         <v>315.351279291574</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="S13" s="2" t="n">
         <v>241.764663458786</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="T13" s="2" t="n">
         <v>241.764663458786</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="U13" s="2" t="n">
         <v>117.50904031122</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="V13" s="2" t="n">
         <v>117.50904031122</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>251.2298503483636</v>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>323.6420722797649</v>
-      </c>
-      <c r="X13" t="n">
-        <v>85.29867757995484</v>
+      <c r="W13" s="2" t="n">
+        <v>246.1340331846991</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>318.395091701414</v>
       </c>
     </row>
     <row r="14">
@@ -3721,59 +3775,63 @@
           <t>Clupeids</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" s="2" t="n">
         <v>139.0360670903112</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
+        <v>62.51718857610121</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>124.0840822817122</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>124.0840822817122</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>121.4783165537962</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>135.6716091572296</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>134.6748361908867</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>134.6748361908867</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>105.2687570410784</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>49.95778973536858</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>134.674836190887</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="R14" s="2" t="n">
         <v>134.674836190887</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="S14" s="2" t="n">
         <v>105.268757041078</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="T14" s="2" t="n">
         <v>105.268757041078</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="U14" s="2" t="n">
         <v>49.9577897353686</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="V14" s="2" t="n">
         <v>49.9577897353686</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>111.0293978994619</v>
-      </c>
-      <c r="V14" s="2" t="n">
-        <v>137.3658946426152</v>
-      </c>
-      <c r="X14" t="n">
-        <v>62.51718857610121</v>
+      <c r="W14" s="2" t="n">
+        <v>106.3718180575102</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>139.4983447156464</v>
       </c>
     </row>
     <row r="15">
@@ -3785,59 +3843,63 @@
           <t>Mackerel</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" s="2" t="n">
         <v>5.557254062071582</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
+        <v>4.359533917665248</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>9.106403715332288</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>9.106403715332288</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>8.924275641025641</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>9.458164835542291</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>9.106403715332288</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>9.106403715332288</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="O15" s="2" t="n">
         <v>8.924275641025641</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>7.139420512820513</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>9.10640371533229</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="R15" s="2" t="n">
         <v>9.10640371533229</v>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="S15" s="2" t="n">
         <v>8.924275641025639</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="T15" s="2" t="n">
         <v>8.924275641025639</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="U15" s="2" t="n">
         <v>7.13942051282051</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="V15" s="2" t="n">
         <v>7.13942051282051</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>9.203798850622503</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>9.142999596962323</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.359533917665248</v>
+      <c r="W15" s="2" t="n">
+        <v>8.881379168881503</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>9.124264705271582</v>
       </c>
     </row>
     <row r="16">
@@ -3849,59 +3911,63 @@
           <t>Small Benthopelagics</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" s="2" t="n">
         <v>728.5926525649658</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
+        <v>254.9523014578453</v>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>919.9061492990342</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>967.2625055351939</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>945.9827304134196</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>1426.864607154702</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>1329.824765342306</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>1329.824765342306</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>864.4110950598683</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>307.9312796705748</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>1329.82476534231</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="R16" s="2" t="n">
         <v>1329.82476534231</v>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="S16" s="2" t="n">
         <v>864.411095059868</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="T16" s="2" t="n">
         <v>864.411095059868</v>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="U16" s="2" t="n">
         <v>307.931279670575</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="V16" s="2" t="n">
         <v>307.931279670575</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>914.2900268270819</v>
-      </c>
-      <c r="V16" s="2" t="n">
-        <v>1401.621854227955</v>
-      </c>
-      <c r="X16" t="n">
-        <v>254.9523014578453</v>
+      <c r="W16" s="2" t="n">
+        <v>899.2792357909057</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>1396.041474980129</v>
       </c>
     </row>
     <row r="17">
@@ -3913,59 +3979,63 @@
           <t>Small Benthic Carnivores</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" s="2" t="n">
         <v>95.79166706484966</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
+        <v>41.09131584504831</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>100.5572347261105</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>100.5572347261105</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>98.44553279686212</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>160.7050613511514</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>140.5366363307951</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>140.5366363307951</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="O17" s="2" t="n">
         <v>72.75019068297163</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>33.14243075260512</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>140.536636330795</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="R17" s="2" t="n">
         <v>140.536636330795</v>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="S17" s="2" t="n">
         <v>72.75019068297161</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="T17" s="2" t="n">
         <v>72.75019068297161</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="U17" s="2" t="n">
         <v>33.1424307526051</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="V17" s="2" t="n">
         <v>33.1424307526051</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>75.91908621081038</v>
-      </c>
-      <c r="V17" s="2" t="n">
-        <v>151.2584807094888</v>
-      </c>
-      <c r="X17" t="n">
-        <v>41.09131584504831</v>
+      <c r="W17" s="2" t="n">
+        <v>73.08553209390777</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>148.1083861727158</v>
       </c>
     </row>
     <row r="18">
@@ -3977,59 +4047,63 @@
           <t>Med Benthic Carnivores</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" s="2" t="n">
         <v>225.140772807137</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
+        <v>94.4422691586573</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>142.3376778995271</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>142.3376778995271</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>139.6332620194361</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>198.2082231056915</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>182.1204687790648</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>182.1204687790648</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>108.5405861887764</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>48.38392126938605</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>182.120468779065</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="R18" s="2" t="n">
         <v>182.120468779065</v>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="S18" s="2" t="n">
         <v>108.540586188776</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="T18" s="2" t="n">
         <v>108.540586188776</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="U18" s="2" t="n">
         <v>48.3839212693861</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="V18" s="2" t="n">
         <v>48.3839212693861</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>115.3583030506615</v>
-      </c>
-      <c r="V18" s="2" t="n">
-        <v>193.4812320887115</v>
-      </c>
-      <c r="X18" t="n">
-        <v>94.4422691586573</v>
+      <c r="W18" s="2" t="n">
+        <v>107.9214176317311</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>190.4517341308873</v>
       </c>
     </row>
     <row r="19">
@@ -4041,59 +4115,63 @@
           <t>Large Benthic Carnivores</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" s="2" t="n">
         <v>610.0910780918889</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
+        <v>220.4948512678794</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>361.1000248236857</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>500.6053147134293</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>490.5932084191606</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>1114.691652144382</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="M19" s="2" t="n">
         <v>1007.820980535666</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>1007.820980535666</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="O19" s="2" t="n">
         <v>587.4688941008945</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>183.115693197487</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>1007.82098053567</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="R19" s="2" t="n">
         <v>1007.82098053567</v>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>587.468894100895</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="T19" s="2" t="n">
         <v>587.468894100895</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="U19" s="2" t="n">
         <v>183.115693197487</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="V19" s="2" t="n">
         <v>183.115693197487</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>618.0099815320281</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>1087.7355054648</v>
-      </c>
-      <c r="X19" t="n">
-        <v>220.4948512678794</v>
+      <c r="W19" s="2" t="n">
+        <v>617.089262862891</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>1087.317307745628</v>
       </c>
     </row>
     <row r="20">
@@ -4105,59 +4183,63 @@
           <t>Large Benthopelagics</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" s="2" t="n">
         <v>1636.44010918869</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
+        <v>473.906881375648</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>891.279786561407</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>940.3808037126553</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>921.5731876384021</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>1918.226528674924</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="M20" s="2" t="n">
         <v>1748.189266202579</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="N20" s="2" t="n">
         <v>1748.189266202579</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="O20" s="2" t="n">
         <v>1029.737657930669</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>282.556114821713</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>1748.18926620258</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="R20" s="2" t="n">
         <v>1748.18926620258</v>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="S20" s="2" t="n">
         <v>1029.73765793067</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="T20" s="2" t="n">
         <v>1029.73765793067</v>
       </c>
-      <c r="S20" s="2" t="n">
+      <c r="U20" s="2" t="n">
         <v>282.556114821713</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="V20" s="2" t="n">
         <v>282.556114821713</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>1121.717009754653</v>
-      </c>
-      <c r="V20" s="2" t="n">
-        <v>1862.209046119513</v>
-      </c>
-      <c r="X20" t="n">
-        <v>473.906881375648</v>
+      <c r="W20" s="2" t="n">
+        <v>1086.561312151374</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>1872.45165670843</v>
       </c>
     </row>
     <row r="21">
@@ -4169,59 +4251,63 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" s="2" t="n">
         <v>1064.398658569565</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
+        <v>347.7981575665012</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>1184.851684023025</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>1187.178421135501</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>1157.498960607114</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>2933.853361777305</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>2688.513881136939</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>2688.513881136939</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>1646.854477109562</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>499.2255799332781</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>2688.51388113694</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>2688.51388113694</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="S21" s="2" t="n">
         <v>1646.85447710956</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="T21" s="2" t="n">
         <v>1646.85447710956</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="U21" s="2" t="n">
         <v>499.225579933278</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="V21" s="2" t="n">
         <v>499.225579933278</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>1741.341956991357</v>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>2896.825960442839</v>
-      </c>
-      <c r="X21" t="n">
-        <v>347.7981575665012</v>
+      <c r="W21" s="2" t="n">
+        <v>1785.092103641393</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>2919.570631846536</v>
       </c>
     </row>
     <row r="22">
@@ -4233,59 +4319,63 @@
           <t>Tunas</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" s="2" t="n">
         <v>972.6576464312997</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
+        <v>333.0254672490636</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>751.7539715348304</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>763.9636075893302</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>537.0664161352991</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>970.7828260845469</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="M22" s="2" t="n">
         <v>920.9356375746706</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>920.9356375746706</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>464.2098371786046</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>164.8769469343089</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>920.935637574671</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="R22" s="2" t="n">
         <v>920.935637574671</v>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="S22" s="2" t="n">
         <v>464.209837178605</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="T22" s="2" t="n">
         <v>464.209837178605</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="U22" s="2" t="n">
         <v>164.876946934309</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="V22" s="2" t="n">
         <v>164.876946934309</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>491.2110994913672</v>
-      </c>
-      <c r="V22" s="2" t="n">
-        <v>949.2664681204172</v>
-      </c>
-      <c r="X22" t="n">
-        <v>333.0254672490636</v>
+      <c r="W22" s="2" t="n">
+        <v>476.0975141062352</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>951.4382132936707</v>
       </c>
     </row>
     <row r="23">
@@ -4297,59 +4387,63 @@
           <t>Large Pelagics</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" s="2" t="n">
         <v>2235.112916068463</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
+        <v>581.4580268409309</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>734.6257685687615</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>765.799237128584</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="K23" s="2" t="n">
         <v>750.4832523860123</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="L23" s="2" t="n">
         <v>1961.116323246852</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="M23" s="2" t="n">
         <v>1774.441652524202</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="N23" s="2" t="n">
         <v>1774.441652524202</v>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="O23" s="2" t="n">
         <v>1010.708909823136</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>249.5986844266526</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>1774.4416525242</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="R23" s="2" t="n">
         <v>1774.4416525242</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="S23" s="2" t="n">
         <v>1010.70890982314</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="T23" s="2" t="n">
         <v>1010.70890982314</v>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="U23" s="2" t="n">
         <v>249.598684426653</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="V23" s="2" t="n">
         <v>249.598684426653</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>1120.189837631029</v>
-      </c>
-      <c r="V23" s="2" t="n">
-        <v>1940.538493448634</v>
-      </c>
-      <c r="X23" t="n">
-        <v>581.4580268409309</v>
+      <c r="W23" s="2" t="n">
+        <v>1087.699765542491</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>1911.038107856712</v>
       </c>
     </row>
     <row r="24">
@@ -4361,59 +4455,63 @@
           <t>Skates &amp; Rays</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" s="2" t="n">
         <v>622.2719892432722</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
+        <v>204.450412950168</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>1723.249235490315</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>1762.472698050895</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>1055.721146132486</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>3126.18566880461</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="M24" s="2" t="n">
         <v>2704.018471858245</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="N24" s="2" t="n">
         <v>2704.018471858245</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="O24" s="2" t="n">
         <v>792.7357946534784</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>276.6430075065673</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>2704.01847185824</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="R24" s="2" t="n">
         <v>2704.01847185824</v>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="S24" s="2" t="n">
         <v>792.735794653479</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="T24" s="2" t="n">
         <v>792.735794653479</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="U24" s="2" t="n">
         <v>276.643007506567</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="V24" s="2" t="n">
         <v>276.643007506567</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>835.8645863619785</v>
-      </c>
-      <c r="V24" s="2" t="n">
-        <v>2884.025385365229</v>
-      </c>
-      <c r="X24" t="n">
-        <v>204.450412950168</v>
+      <c r="W24" s="2" t="n">
+        <v>814.691327010602</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>2880.227701636903</v>
       </c>
     </row>
     <row r="25">
@@ -4425,59 +4523,63 @@
           <t>Sharks</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" s="2" t="n">
         <v>5105.589709036698</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
+        <v>1164.579641210795</v>
+      </c>
+      <c r="I25" s="2" t="n">
         <v>1695.298486256927</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>1742.678367097115</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>1235.558962271855</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="L25" s="2" t="n">
         <v>3930.042293288787</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="M25" s="2" t="n">
         <v>3557.676394227331</v>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="N25" s="2" t="n">
         <v>3557.676394227331</v>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="O25" s="2" t="n">
         <v>1462.857104528249</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>343.9109690994405</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>3557.67639422733</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="R25" s="2" t="n">
         <v>3557.67639422733</v>
       </c>
-      <c r="Q25" s="2" t="n">
+      <c r="S25" s="2" t="n">
         <v>1462.85710452825</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="T25" s="2" t="n">
         <v>1462.85710452825</v>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="U25" s="2" t="n">
         <v>343.910969099441</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="V25" s="2" t="n">
         <v>343.910969099441</v>
       </c>
-      <c r="U25" s="2" t="n">
-        <v>1592.095409027788</v>
-      </c>
-      <c r="V25" s="2" t="n">
-        <v>3847.70452912626</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1164.579641210795</v>
+      <c r="W25" s="2" t="n">
+        <v>1568.545717284607</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>3849.264948471274</v>
       </c>
     </row>
     <row r="26">
@@ -4489,59 +4591,63 @@
           <t>Marine Mammals</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" s="2" t="n">
         <v>1210.393037299881</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
+        <v>367.4916040090425</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>215540.4465025496</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>228489.751428647</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="K26" s="2" t="n">
         <v>11652.97732286101</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="L26" s="2" t="n">
         <v>493549.2649017496</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="M26" s="2" t="n">
         <v>442889.7326164861</v>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>442889.7326164861</v>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="O26" s="2" t="n">
         <v>13068.84072294853</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>3605.476706643315</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>442889.732616486</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="R26" s="2" t="n">
         <v>442889.732616486</v>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="S26" s="2" t="n">
         <v>13068.8407229485</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="T26" s="2" t="n">
         <v>13068.8407229485</v>
       </c>
-      <c r="S26" s="2" t="n">
+      <c r="U26" s="2" t="n">
         <v>3605.47670664331</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="V26" s="2" t="n">
         <v>3605.47670664331</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>13584.92612517964</v>
-      </c>
-      <c r="V26" s="2" t="n">
-        <v>475505.0514294247</v>
-      </c>
-      <c r="X26" t="n">
-        <v>367.4916040090425</v>
+      <c r="W26" s="2" t="n">
+        <v>14018.59961098725</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>483246.2433649153</v>
       </c>
     </row>
   </sheetData>
@@ -4580,6 +4686,8 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4610,97 +4718,97 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Ulanowicz_globalTEmean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ulanowicz_TE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EwE_TE_noEE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>EwE_TE_EE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>SPPR_2015</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>new_TE_noEEfix</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>new_TE_EEfix</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>new_GE</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>new_WithEgestion</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>sym_TE_asPP</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sym_TE_asDC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>sym_GE_asPP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>sym_GE_asDC</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sym_WithEgestion_asPP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>sym_WithEgestion_asDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MC_new_GE</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>SPPR_1995_TEmean_catch</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -4752,22 +4860,25 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4796,55 +4907,55 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.3223803903634934</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.3223803903634934</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0.3223803903634934</v>
       </c>
       <c r="M3" s="2" t="n">
+        <v>0.3223803903634934</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.3223803903634934</v>
+      </c>
+      <c r="O3" s="2" t="n">
         <v>2.223716817046537</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>3.699779449329617</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>0.3223803903634934</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>0.3223803903634934</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>2.223716817046537</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="T3" s="2" t="n">
         <v>2.223716817046537</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="U3" s="2" t="n">
         <v>3.699779449329617</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="V3" s="2" t="n">
         <v>3.699779449329617</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>2.307206660370829</v>
-      </c>
-      <c r="V3" s="2" t="n">
+      <c r="W3" s="2" t="n">
+        <v>2.303349321428358</v>
+      </c>
+      <c r="X3" s="2" t="n">
         <v>0.3223803903634925</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4872,17 +4983,17 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.842</v>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
@@ -4916,10 +5027,10 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="W4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4942,61 +5053,61 @@
         <v>6.223128848904347</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>6.223128848904347</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>5.102040816326531</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>5.102040816326531</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5.102040816326531</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>5.102040816326531</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>5.102040816326531</v>
       </c>
       <c r="M5" s="2" t="n">
+        <v>5.102040816326531</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>5.102040816326531</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>5.10204081632653</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>5.10204081632653</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="V5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>5.036055358031964</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>5.124599030923125</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.881896884283592</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.881896884283592</v>
+      <c r="W5" s="2" t="n">
+        <v>5.027068645578732</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>5.123573062782874</v>
       </c>
     </row>
     <row r="6">
@@ -5018,61 +5129,61 @@
         <v>18.10130675474342</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>12.32322407924027</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>25.20558388046248</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
+        <v>15.94929274210823</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>21.82880466472303</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>22.27429047420718</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>21.44571428571428</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>14.15314285714286</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>22.2742904742072</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>22.2742904742072</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>21.4457142857143</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="T6" s="2" t="n">
         <v>21.4457142857143</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="U6" s="2" t="n">
         <v>14.1531428571429</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="V6" s="2" t="n">
         <v>14.1531428571429</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>21.7943514061429</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>22.32385000367074</v>
-      </c>
-      <c r="W6" t="n">
-        <v>12.32322407924027</v>
-      </c>
-      <c r="X6" t="n">
-        <v>15.94929274210823</v>
+      <c r="W6" s="2" t="n">
+        <v>21.44097580734458</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>22.18757739942376</v>
       </c>
     </row>
     <row r="7">
@@ -5094,61 +5205,61 @@
         <v>58.79467325663467</v>
       </c>
       <c r="F7" s="2" t="n">
+        <v>34.23132986499605</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>103.84897625005</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
+        <v>53.05644145839639</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>117.6812039542221</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>117.6812039542221</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>91.55597667638483</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>131.1429729548547</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>131.1429729548547</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>131.1429729548547</v>
       </c>
       <c r="M7" s="2" t="n">
+        <v>131.1429729548547</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>131.1429729548547</v>
+      </c>
+      <c r="O7" s="2" t="n">
         <v>96.50135934104082</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>51.76544661134316</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>131.1429729548545</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>131.1429729548545</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>96.50135934104084</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>96.50135934104084</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>51.76544661134319</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="V7" s="2" t="n">
         <v>51.76544661134319</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>100.4023602014547</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>135.3221220669738</v>
-      </c>
-      <c r="W7" t="n">
-        <v>34.23132986499605</v>
-      </c>
-      <c r="X7" t="n">
-        <v>53.05644145839639</v>
+      <c r="W7" s="2" t="n">
+        <v>96.51137193611446</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>132.9276808818918</v>
       </c>
     </row>
     <row r="8">
@@ -5170,61 +5281,61 @@
         <v>6.246415572627058</v>
       </c>
       <c r="F8" s="2" t="n">
+        <v>4.897735417991635</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>6.157451550719678</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
+        <v>4.817279090322625</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>8.469311156097827</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>8.469311156097827</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>3.15905306122449</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>3.409782525859228</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>3.409782525859229</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>3.409782525859229</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>7.483182207332487</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>9.793668562856155</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>3.409782525859238</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>3.409782525859239</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>7.483182207332487</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="T8" s="2" t="n">
         <v>7.483182207332487</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="U8" s="2" t="n">
         <v>9.793668562856155</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="V8" s="2" t="n">
         <v>9.793668562856155</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>7.934972432878392</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>3.463436398110999</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.897735417991635</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.817279090322625</v>
+      <c r="W8" s="2" t="n">
+        <v>7.981693245792052</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>3.491457020594954</v>
       </c>
     </row>
     <row r="9">
@@ -5246,61 +5357,61 @@
         <v>10.76764438018142</v>
       </c>
       <c r="F9" s="2" t="n">
+        <v>7.853920505552195</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>22.43097915721846</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
+        <v>13.27020707414865</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>123.8880416542777</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>123.8880416542777</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>15.36211716513043</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>260.72059691995</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>260.7205969199499</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>260.7205969199499</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>19.31401817983195</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>17.70369623887368</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>260.7205969199497</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>260.7205969199497</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>19.31401817983196</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>19.31401817983196</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>17.70369623887368</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="V9" s="2" t="n">
         <v>17.70369623887368</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>19.98890558776613</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>287.8073165313254</v>
-      </c>
-      <c r="W9" t="n">
-        <v>7.853920505552195</v>
-      </c>
-      <c r="X9" t="n">
-        <v>13.27020707414865</v>
+      <c r="W9" s="2" t="n">
+        <v>19.98415203222996</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>280.3920237374933</v>
       </c>
     </row>
     <row r="10">
@@ -5322,61 +5433,61 @@
         <v>16.77111671055687</v>
       </c>
       <c r="F10" s="2" t="n">
+        <v>11.53393332626138</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>46.13615066233237</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
+        <v>23.95459789823945</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>122.1105836808597</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>122.1105836808596</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>119.6683720072425</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>234.3262107631635</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>234.3262107631634</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>234.3262107631634</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>32.57439609705445</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>28.19192747429306</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>234.3262107631637</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="R10" s="2" t="n">
         <v>234.3262107631637</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="S10" s="2" t="n">
         <v>32.57439609705445</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="T10" s="2" t="n">
         <v>32.57439609705445</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="U10" s="2" t="n">
         <v>28.19192747429308</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="V10" s="2" t="n">
         <v>28.19192747429308</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>33.18357929041669</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>263.2496245661334</v>
-      </c>
-      <c r="W10" t="n">
-        <v>11.53393332626138</v>
-      </c>
-      <c r="X10" t="n">
-        <v>23.95459789823945</v>
+      <c r="W10" s="2" t="n">
+        <v>34.1102848740697</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>254.340856720556</v>
       </c>
     </row>
     <row r="11">
@@ -5398,61 +5509,61 @@
         <v>39.56283070651072</v>
       </c>
       <c r="F11" s="2" t="n">
+        <v>24.27818587440447</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>98.6116966075774</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
+        <v>49.2544955448092</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>47.33250285039934</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>47.33250285039934</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>46.38585279339136</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>49.86108608645311</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>49.8610860864531</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>49.8610860864531</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>41.27778681628659</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="P11" s="2" t="n">
         <v>24.79345222836741</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>49.86108608645308</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="R11" s="2" t="n">
         <v>49.86108608645308</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="S11" s="2" t="n">
         <v>41.2777868162866</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="T11" s="2" t="n">
         <v>41.2777868162866</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="U11" s="2" t="n">
         <v>24.79345222836744</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="V11" s="2" t="n">
         <v>24.79345222836744</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>42.88468344234155</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>51.83930781587688</v>
-      </c>
-      <c r="W11" t="n">
-        <v>24.27818587440447</v>
-      </c>
-      <c r="X11" t="n">
-        <v>49.2544955448092</v>
+      <c r="W11" s="2" t="n">
+        <v>41.64390446764779</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>50.99219905009992</v>
       </c>
     </row>
     <row r="12">
@@ -5474,61 +5585,61 @@
         <v>30.94067580555833</v>
       </c>
       <c r="F12" s="2" t="n">
+        <v>19.61701044712016</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>88.6615481068378</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
+        <v>40.48007979745215</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>77.81175772311749</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>77.81175772311748</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>75.94427553776266</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>117.553731679799</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>117.553731679799</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>117.553731679799</v>
       </c>
       <c r="M12" s="2" t="n">
+        <v>117.553731679799</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>117.553731679799</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>38.10954179367167</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>24.77877022156451</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>117.553731679799</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="R12" s="2" t="n">
         <v>117.553731679799</v>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="S12" s="2" t="n">
         <v>38.10954179367167</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="T12" s="2" t="n">
         <v>38.10954179367167</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="U12" s="2" t="n">
         <v>24.7787702215645</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="V12" s="2" t="n">
         <v>24.7787702215645</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>40.04113192877045</v>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>130.2728115138363</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.61701044712016</v>
-      </c>
-      <c r="X12" t="n">
-        <v>40.48007979745215</v>
+      <c r="W12" s="2" t="n">
+        <v>39.66729446369943</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>124.3612134251785</v>
       </c>
     </row>
     <row r="13">
@@ -5550,61 +5661,61 @@
         <v>94.17864685117233</v>
       </c>
       <c r="F13" s="2" t="n">
+        <v>51.50764169239473</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>186.9483287457134</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
+        <v>86.24822714450288</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>292.9935734046114</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>292.9935734046113</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>286.2547212163053</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>324.4406618972106</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>324.4406618972105</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>324.4406618972105</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>245.2514018961825</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>121.200331417889</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>324.4406618972104</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="R13" s="2" t="n">
         <v>324.4406618972104</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="S13" s="2" t="n">
         <v>245.251401896183</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="T13" s="2" t="n">
         <v>245.251401896183</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="U13" s="2" t="n">
         <v>121.2003314178887</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="V13" s="2" t="n">
         <v>121.2003314178887</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>254.9540560991221</v>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>333.7708523617817</v>
-      </c>
-      <c r="W13" t="n">
-        <v>51.50764169239473</v>
-      </c>
-      <c r="X13" t="n">
-        <v>86.24822714450288</v>
+      <c r="W13" s="2" t="n">
+        <v>249.8641182762686</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>328.2413106004485</v>
       </c>
     </row>
     <row r="14">
@@ -5626,61 +5737,61 @@
         <v>35.16658028962565</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>21.9205342021058</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>139.9688809708051</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
+        <v>63.18533145172209</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>125.5029051695527</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>125.5029051695527</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>122.8673441609921</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>135.6716091572296</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>135.6716091572295</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>135.6716091572295</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>106.9624779872631</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>52.04542467740351</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>135.6716091572299</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="R14" s="2" t="n">
         <v>135.6716091572299</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="S14" s="2" t="n">
         <v>106.9624779872628</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="T14" s="2" t="n">
         <v>106.9624779872628</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="U14" s="2" t="n">
         <v>52.04542467740354</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="V14" s="2" t="n">
         <v>52.04542467740354</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>112.8441450348056</v>
-      </c>
-      <c r="V14" s="2" t="n">
-        <v>138.4479745464489</v>
-      </c>
-      <c r="W14" t="n">
-        <v>21.9205342021058</v>
-      </c>
-      <c r="X14" t="n">
-        <v>63.18533145172209</v>
+      <c r="W14" s="2" t="n">
+        <v>108.1498347722911</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>140.5830492930381</v>
       </c>
     </row>
     <row r="15">
@@ -5702,61 +5813,61 @@
         <v>6.223128848904347</v>
       </c>
       <c r="F15" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>6.223128848904347</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>10.19754055468341</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>10.19754055468341</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>9.993589743589745</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>9.458164835542291</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>9.458164835542291</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>9.458164835542291</v>
       </c>
       <c r="M15" s="2" t="n">
+        <v>9.458164835542291</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>9.458164835542291</v>
+      </c>
+      <c r="O15" s="2" t="n">
         <v>11.30212739360246</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>10.30440158605652</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>9.458164835542295</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="R15" s="2" t="n">
         <v>9.458164835542295</v>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="S15" s="2" t="n">
         <v>11.30212739360245</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="T15" s="2" t="n">
         <v>11.30212739360245</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="U15" s="2" t="n">
         <v>10.30440158605652</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="V15" s="2" t="n">
         <v>10.30440158605652</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>11.75413197094962</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>9.496174338698417</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.881896884283592</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.881896884283592</v>
+      <c r="W15" s="2" t="n">
+        <v>11.33548858150522</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>9.476715757756224</v>
       </c>
     </row>
     <row r="16">
@@ -5778,61 +5889,61 @@
         <v>188.9246547467871</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>94.20345180303136</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>772.3589140731528</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
+        <v>274.1184846161911</v>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>1003.748472342274</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>1056.007849028164</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>1032.775676349545</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>1426.864607154702</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>1426.864607154701</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>1426.864607154701</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>914.129060439588</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>345.8704013120807</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>1426.864607154705</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="R16" s="2" t="n">
         <v>1426.864607154705</v>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="S16" s="2" t="n">
         <v>914.1290604395878</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="T16" s="2" t="n">
         <v>914.1290604395878</v>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="U16" s="2" t="n">
         <v>345.870401312081</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="V16" s="2" t="n">
         <v>345.870401312081</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>967.8774022465338</v>
-      </c>
-      <c r="V16" s="2" t="n">
-        <v>1512.932250311565</v>
-      </c>
-      <c r="W16" t="n">
-        <v>94.20345180303136</v>
-      </c>
-      <c r="X16" t="n">
-        <v>274.1184846161911</v>
+      <c r="W16" s="2" t="n">
+        <v>953.8731660379115</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>1505.581654613894</v>
       </c>
     </row>
     <row r="17">
@@ -5854,61 +5965,61 @@
         <v>21.57858629762915</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>14.35176635029988</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>107.4629161326766</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
+        <v>47.93631306284109</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>123.6827696735525</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>123.6827696735525</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>121.0854315104078</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>160.7050613511514</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>160.7050613511513</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>160.7050613511513</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="O17" s="2" t="n">
         <v>86.69574979544262</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>48.55112208776874</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>160.7050613511512</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="R17" s="2" t="n">
         <v>160.7050613511512</v>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="S17" s="2" t="n">
         <v>86.69574979544259</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="T17" s="2" t="n">
         <v>86.69574979544259</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="U17" s="2" t="n">
         <v>48.55112208776875</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="V17" s="2" t="n">
         <v>48.55112208776875</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>90.59454197909548</v>
-      </c>
-      <c r="V17" s="2" t="n">
-        <v>174.3038165894203</v>
-      </c>
-      <c r="W17" t="n">
-        <v>14.35176635029988</v>
-      </c>
-      <c r="X17" t="n">
-        <v>47.93631306284109</v>
+      <c r="W17" s="2" t="n">
+        <v>87.80902547171854</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>170.4358031713677</v>
       </c>
     </row>
     <row r="18">
@@ -5927,64 +6038,64 @@
         <v>153.5063191216989</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>54.42563084569721</v>
+        <v>54.42563084569726</v>
       </c>
       <c r="F18" s="2" t="n">
+        <v>32.01412407426785</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>236.6828022651465</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
+        <v>100.6878204145854</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>159.0613711885023</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>159.0613711885023</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>156.0392051359208</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>198.2082231056915</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>198.2082231056914</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>198.2082231056914</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>116.373231289557</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>56.49052560682633</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>198.2082231056916</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="R18" s="2" t="n">
         <v>198.2082231056916</v>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="S18" s="2" t="n">
         <v>116.3732312895566</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="T18" s="2" t="n">
         <v>116.3732312895566</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="U18" s="2" t="n">
         <v>56.49052560682637</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="V18" s="2" t="n">
         <v>56.49052560682637</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>123.7092022756005</v>
-      </c>
-      <c r="V18" s="2" t="n">
-        <v>211.8709226329803</v>
-      </c>
-      <c r="W18" t="n">
-        <v>32.01412407426783</v>
-      </c>
-      <c r="X18" t="n">
-        <v>100.6878204145854</v>
+      <c r="W18" s="2" t="n">
+        <v>116.1399239726856</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>208.3211052502791</v>
       </c>
     </row>
     <row r="19">
@@ -6006,61 +6117,61 @@
         <v>262.4070949788439</v>
       </c>
       <c r="F19" s="2" t="n">
+        <v>125.2590957378396</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>672.1889581826362</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
+        <v>249.9812478195048</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>421.7498448185209</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>575.6382317549858</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>564.125467119886</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>1114.691652144382</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1114.691652144382</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>1114.691652144382</v>
       </c>
       <c r="M19" s="2" t="n">
+        <v>1114.691652144382</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1114.691652144382</v>
+      </c>
+      <c r="O19" s="2" t="n">
         <v>635.9376562683256</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>217.2386746189102</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>1114.691652144385</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="R19" s="2" t="n">
         <v>1114.691652144385</v>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>635.9376562683261</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="T19" s="2" t="n">
         <v>635.9376562683261</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="U19" s="2" t="n">
         <v>217.2386746189103</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="V19" s="2" t="n">
         <v>217.2386746189103</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>669.7421522924902</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>1212.57805917571</v>
-      </c>
-      <c r="W19" t="n">
-        <v>125.2590957378396</v>
-      </c>
-      <c r="X19" t="n">
-        <v>249.9812478195048</v>
+      <c r="W19" s="2" t="n">
+        <v>670.5654263315668</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>1209.82486843931</v>
       </c>
     </row>
     <row r="20">
@@ -6082,61 +6193,61 @@
         <v>288.507746425553</v>
       </c>
       <c r="F20" s="2" t="n">
+        <v>135.9951668482977</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>1782.49431863192</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
+        <v>530.8757765188035</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>1013.570171471442</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>1067.730871536711</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>1046.376254105977</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1918.226528674924</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1918.226528674924</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1918.226528674924</v>
       </c>
       <c r="M20" s="2" t="n">
+        <v>1918.226528674924</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1918.226528674924</v>
+      </c>
+      <c r="O20" s="2" t="n">
         <v>1111.682877581138</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>334.6245073550722</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>1918.226528674925</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="R20" s="2" t="n">
         <v>1918.226528674925</v>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="S20" s="2" t="n">
         <v>1111.682877581138</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="T20" s="2" t="n">
         <v>1111.682877581138</v>
       </c>
-      <c r="S20" s="2" t="n">
+      <c r="U20" s="2" t="n">
         <v>334.624507355072</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="V20" s="2" t="n">
         <v>334.624507355072</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>1212.403983721935</v>
-      </c>
-      <c r="V20" s="2" t="n">
-        <v>2057.246558511828</v>
-      </c>
-      <c r="W20" t="n">
-        <v>135.9951668482977</v>
-      </c>
-      <c r="X20" t="n">
-        <v>530.8757765188035</v>
+      <c r="W20" s="2" t="n">
+        <v>1177.252795758544</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>2066.176882794377</v>
       </c>
     </row>
     <row r="21">
@@ -6158,61 +6269,61 @@
         <v>288.5103905458261</v>
       </c>
       <c r="F21" s="2" t="n">
+        <v>135.996247738189</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>1152.508392338651</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
+        <v>384.9639588136019</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>1331.752693342869</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>1334.2572945693</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>1300.900862205068</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>2933.853361777305</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>2933.853361777304</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>2933.853361777304</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>1771.038679713454</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>582.8715320516791</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>2933.853361777306</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>2933.853361777306</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="S21" s="2" t="n">
         <v>1771.038679713452</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="T21" s="2" t="n">
         <v>1771.038679713452</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="U21" s="2" t="n">
         <v>582.8715320516792</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="V21" s="2" t="n">
         <v>582.8715320516792</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>1875.159902155221</v>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>3182.729383356123</v>
-      </c>
-      <c r="W21" t="n">
-        <v>135.996247738189</v>
-      </c>
-      <c r="X21" t="n">
-        <v>384.9639588136019</v>
+      <c r="W21" s="2" t="n">
+        <v>1926.989095139347</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>3204.045693303023</v>
       </c>
     </row>
     <row r="22">
@@ -6231,64 +6342,64 @@
         <v>1377.951482341825</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>310.8703778357537</v>
+        <v>310.8703778357543</v>
       </c>
       <c r="F22" s="2" t="n">
+        <v>145.0910757257476</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>1019.11674600522</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
+        <v>354.0160885041838</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>804.6273553053973</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>818.1011108998474</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>575.1250809625926</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>970.7828260845469</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="M22" s="2" t="n">
         <v>970.7828260845463</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>970.7828260845463</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>487.0569072979667</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>182.8633148377885</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>970.7828260845465</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="R22" s="2" t="n">
         <v>970.7828260845465</v>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="S22" s="2" t="n">
         <v>487.0569072979672</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="T22" s="2" t="n">
         <v>487.0569072979672</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="U22" s="2" t="n">
         <v>182.8633148377886</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="V22" s="2" t="n">
         <v>182.8633148377886</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>515.9272814041871</v>
-      </c>
-      <c r="V22" s="2" t="n">
-        <v>1005.016369881499</v>
-      </c>
-      <c r="W22" t="n">
-        <v>145.0910757257474</v>
-      </c>
-      <c r="X22" t="n">
-        <v>354.0160885041838</v>
+      <c r="W22" s="2" t="n">
+        <v>500.6265281280895</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>1006.613772155264</v>
       </c>
     </row>
     <row r="23">
@@ -6310,61 +6421,61 @@
         <v>275.3006232985392</v>
       </c>
       <c r="F23" s="2" t="n">
+        <v>130.5795261988503</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>2443.4114085821</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
+        <v>655.0984682910046</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>848.8851915781844</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>883.2611115348235</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="K23" s="2" t="n">
         <v>865.595889304127</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>1961.116323246852</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>1961.116323246852</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>1961.116323246852</v>
       </c>
       <c r="M23" s="2" t="n">
+        <v>1961.116323246852</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1961.116323246852</v>
+      </c>
+      <c r="O23" s="2" t="n">
         <v>1097.797369118902</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>300.8034198641895</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>1961.11632324685</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="R23" s="2" t="n">
         <v>1961.11632324685</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="S23" s="2" t="n">
         <v>1097.797369118906</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="T23" s="2" t="n">
         <v>1097.797369118906</v>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="U23" s="2" t="n">
         <v>300.8034198641898</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="V23" s="2" t="n">
         <v>300.8034198641898</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>1217.954800512522</v>
-      </c>
-      <c r="V23" s="2" t="n">
-        <v>2161.079708508654</v>
-      </c>
-      <c r="W23" t="n">
-        <v>130.5795261988503</v>
-      </c>
-      <c r="X23" t="n">
-        <v>655.0984682910046</v>
+      <c r="W23" s="2" t="n">
+        <v>1185.911313165701</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>2124.01878375962</v>
       </c>
     </row>
     <row r="24">
@@ -6386,61 +6497,61 @@
         <v>111.320330100519</v>
       </c>
       <c r="F24" s="2" t="n">
+        <v>59.54587886365636</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>691.0777210943435</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
+        <v>236.0536915685313</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>2128.450324204537</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>2171.723686015249</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>1300.862487923134</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>3126.18566880461</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>3126.18566880461</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>3126.18566880461</v>
       </c>
       <c r="M24" s="2" t="n">
+        <v>3126.18566880461</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>3126.18566880461</v>
+      </c>
+      <c r="O24" s="2" t="n">
         <v>887.6343072748797</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>357.5420041753196</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>3126.185668804606</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="R24" s="2" t="n">
         <v>3126.185668804606</v>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="S24" s="2" t="n">
         <v>887.6343072748805</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="T24" s="2" t="n">
         <v>887.6343072748805</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="U24" s="2" t="n">
         <v>357.5420041753196</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="V24" s="2" t="n">
         <v>357.5420041753196</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>937.0141323326557</v>
-      </c>
-      <c r="V24" s="2" t="n">
-        <v>3360.569290714359</v>
-      </c>
-      <c r="W24" t="n">
-        <v>59.54587886365636</v>
-      </c>
-      <c r="X24" t="n">
-        <v>236.0536915685313</v>
+      <c r="W24" s="2" t="n">
+        <v>916.7585913209008</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>3351.353169810148</v>
       </c>
     </row>
     <row r="25">
@@ -6462,61 +6573,61 @@
         <v>509.8254375061286</v>
       </c>
       <c r="F25" s="2" t="n">
+        <v>222.8221513847066</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>5573.824861515769</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
+        <v>1308.685036527036</v>
+      </c>
+      <c r="I25" s="2" t="n">
         <v>1955.186859493807</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>2007.418174584036</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>1423.259485780082</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>3930.042293288787</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>3930.042293288787</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>3930.042293288787</v>
       </c>
       <c r="M25" s="2" t="n">
+        <v>3930.042293288787</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>3930.042293288787</v>
+      </c>
+      <c r="O25" s="2" t="n">
         <v>1585.345045082565</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>411.2685218988508</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>3930.042293288785</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="R25" s="2" t="n">
         <v>3930.042293288785</v>
       </c>
-      <c r="Q25" s="2" t="n">
+      <c r="S25" s="2" t="n">
         <v>1585.345045082566</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="T25" s="2" t="n">
         <v>1585.345045082566</v>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="U25" s="2" t="n">
         <v>411.2685218988514</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="V25" s="2" t="n">
         <v>411.2685218988514</v>
       </c>
-      <c r="U25" s="2" t="n">
-        <v>1727.014599662814</v>
-      </c>
-      <c r="V25" s="2" t="n">
-        <v>4280.685882503204</v>
-      </c>
-      <c r="W25" t="n">
-        <v>222.8221513847066</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1308.685036527036</v>
+      <c r="W25" s="2" t="n">
+        <v>1706.163340653995</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>4274.319993004987</v>
       </c>
     </row>
     <row r="26">
@@ -6538,61 +6649,61 @@
         <v>261.195153950476</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>124.757235171582</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>1335.321685246217</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
+        <v>418.7723011987895</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>255333.6498407797</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>269612.5273851222</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="K26" s="2" t="n">
         <v>13750.23889664124</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>493549.2649017496</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>493549.2649017496</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>493549.2649017496</v>
       </c>
       <c r="M26" s="2" t="n">
+        <v>493549.2649017496</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>493549.2649017496</v>
+      </c>
+      <c r="O26" s="2" t="n">
         <v>14395.8984571961</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>4511.0569155873</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>493549.2649017493</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="R26" s="2" t="n">
         <v>493549.2649017493</v>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="S26" s="2" t="n">
         <v>14395.89845719607</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="T26" s="2" t="n">
         <v>14395.89845719607</v>
       </c>
-      <c r="S26" s="2" t="n">
+      <c r="U26" s="2" t="n">
         <v>4511.056915587296</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="V26" s="2" t="n">
         <v>4511.056915587296</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>14978.82322944805</v>
-      </c>
-      <c r="V26" s="2" t="n">
-        <v>533729.0919429567</v>
-      </c>
-      <c r="W26" t="n">
-        <v>124.757235171582</v>
-      </c>
-      <c r="X26" t="n">
-        <v>418.7723011987895</v>
+      <c r="W26" s="2" t="n">
+        <v>15498.8073599569</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>541558.1880342518</v>
       </c>
     </row>
   </sheetData>
@@ -6631,6 +6742,8 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6661,97 +6774,97 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Ulanowicz_globalTEmean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ulanowicz_TE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EwE_TE_noEE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>EwE_TE_EE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>SPPR_2015</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>new_TE_noEEfix</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>new_TE_EEfix</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>new_GE</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>new_WithEgestion</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>sym_TE_asPP</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sym_TE_asDC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>sym_GE_asPP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>sym_GE_asDC</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sym_WithEgestion_asPP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>sym_WithEgestion_asDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MC_new_GE</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>SPPR_1995_TEmean_catch</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -6780,16 +6893,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>1</v>
@@ -6803,22 +6916,25 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6847,55 +6963,55 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.3223803903634934</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.3223803903634934</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0.3223803903634934</v>
       </c>
       <c r="M3" s="2" t="n">
+        <v>0.3223803903634934</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.3223803903634934</v>
+      </c>
+      <c r="O3" s="2" t="n">
         <v>2.223716817046537</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>3.699779449329617</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>0.3223803903634934</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>0.3223803903634934</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>2.223716817046537</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="T3" s="2" t="n">
         <v>2.223716817046537</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="U3" s="2" t="n">
         <v>3.699779449329617</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="V3" s="2" t="n">
         <v>3.699779449329617</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>2.307206660370829</v>
-      </c>
-      <c r="V3" s="2" t="n">
+      <c r="W3" s="2" t="n">
+        <v>2.303349321428358</v>
+      </c>
+      <c r="X3" s="2" t="n">
         <v>0.3223803903634925</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -6923,17 +7039,17 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.842</v>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
@@ -6967,10 +7083,10 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="W4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6993,61 +7109,61 @@
         <v>6.223128848904347</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>6.223128848904347</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>5.102040816326531</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>5.102040816326531</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5.102040816326531</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>5.102040816326531</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>5.102040816326531</v>
       </c>
       <c r="M5" s="2" t="n">
+        <v>5.102040816326531</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>5.102040816326531</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>5.10204081632653</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>5.10204081632653</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="V5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>5.036055358031964</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>5.124599030923125</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.881896884283592</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.881896884283592</v>
+      <c r="W5" s="2" t="n">
+        <v>5.027068645578732</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>5.123573062782874</v>
       </c>
     </row>
     <row r="6">
@@ -7069,61 +7185,61 @@
         <v>18.10130675474342</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>12.32322407924027</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>25.20558388046248</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
+        <v>15.94929274210823</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>21.82880466472303</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>22.27429047420718</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>22.27429047420717</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>21.44571428571428</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>14.15314285714286</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>22.2742904742072</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>22.2742904742072</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>21.4457142857143</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="T6" s="2" t="n">
         <v>21.4457142857143</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="U6" s="2" t="n">
         <v>14.1531428571429</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="V6" s="2" t="n">
         <v>14.1531428571429</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>21.7943514061429</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>22.32385000367074</v>
-      </c>
-      <c r="W6" t="n">
-        <v>12.32322407924027</v>
-      </c>
-      <c r="X6" t="n">
-        <v>15.94929274210823</v>
+      <c r="W6" s="2" t="n">
+        <v>21.44097580734458</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>22.18757739942376</v>
       </c>
     </row>
     <row r="7">
@@ -7145,61 +7261,61 @@
         <v>58.79467325663467</v>
       </c>
       <c r="F7" s="2" t="n">
+        <v>34.23132986499605</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>103.84897625005</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
+        <v>53.05644145839639</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>117.6812039542221</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>117.6812039542221</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>91.55597667638483</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>131.1429729548547</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>131.1429729548547</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>131.1429729548547</v>
       </c>
       <c r="M7" s="2" t="n">
+        <v>131.1429729548547</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>131.1429729548547</v>
+      </c>
+      <c r="O7" s="2" t="n">
         <v>96.50135934104082</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>51.76544661134316</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>131.1429729548545</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>131.1429729548545</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>96.50135934104084</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>96.50135934104084</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>51.76544661134319</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="V7" s="2" t="n">
         <v>51.76544661134319</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>100.4023602014547</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>135.3221220669738</v>
-      </c>
-      <c r="W7" t="n">
-        <v>34.23132986499605</v>
-      </c>
-      <c r="X7" t="n">
-        <v>53.05644145839639</v>
+      <c r="W7" s="2" t="n">
+        <v>96.51137193611446</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>132.9276808818918</v>
       </c>
     </row>
     <row r="8">
@@ -7221,61 +7337,61 @@
         <v>6.246415572627058</v>
       </c>
       <c r="F8" s="2" t="n">
+        <v>4.897735417991635</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>6.157451550719678</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
+        <v>4.817279090322625</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>8.469311156097827</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>8.469311156097827</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>3.15905306122449</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>3.409782525859228</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>3.409782525859229</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>3.409782525859229</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>7.483182207332487</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>9.793668562856155</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>3.409782525859238</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>3.409782525859239</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>7.483182207332487</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="T8" s="2" t="n">
         <v>7.483182207332487</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="U8" s="2" t="n">
         <v>9.793668562856155</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="V8" s="2" t="n">
         <v>9.793668562856155</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>7.934972432878392</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>3.463436398110999</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.897735417991635</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.817279090322625</v>
+      <c r="W8" s="2" t="n">
+        <v>7.981693245792052</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>3.491457020594954</v>
       </c>
     </row>
     <row r="9">
@@ -7297,61 +7413,61 @@
         <v>10.76764438018142</v>
       </c>
       <c r="F9" s="2" t="n">
+        <v>7.853920505552195</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>22.43097915721846</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
+        <v>13.27020707414865</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>123.8880416542777</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>123.8880416542777</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>15.36211716513043</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>260.72059691995</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>260.7205969199499</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>260.7205969199499</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>19.31401817983195</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>17.70369623887368</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>260.7205969199497</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>260.7205969199497</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>19.31401817983196</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>19.31401817983196</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>17.70369623887368</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="V9" s="2" t="n">
         <v>17.70369623887368</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>19.98890558776613</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>287.8073165313254</v>
-      </c>
-      <c r="W9" t="n">
-        <v>7.853920505552195</v>
-      </c>
-      <c r="X9" t="n">
-        <v>13.27020707414865</v>
+      <c r="W9" s="2" t="n">
+        <v>19.98415203222996</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>280.3920237374933</v>
       </c>
     </row>
     <row r="10">
@@ -7373,61 +7489,61 @@
         <v>16.77111671055687</v>
       </c>
       <c r="F10" s="2" t="n">
+        <v>11.53393332626138</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>46.13615066233237</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
+        <v>23.95459789823945</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>122.1105836808597</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>122.1105836808596</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>119.6683720072425</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>234.3262107631635</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>234.3262107631634</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>234.3262107631634</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>32.57439609705445</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>28.19192747429306</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>234.3262107631637</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="R10" s="2" t="n">
         <v>234.3262107631637</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="S10" s="2" t="n">
         <v>32.57439609705445</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="T10" s="2" t="n">
         <v>32.57439609705445</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="U10" s="2" t="n">
         <v>28.19192747429308</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="V10" s="2" t="n">
         <v>28.19192747429308</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>33.18357929041669</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>263.2496245661334</v>
-      </c>
-      <c r="W10" t="n">
-        <v>11.53393332626138</v>
-      </c>
-      <c r="X10" t="n">
-        <v>23.95459789823945</v>
+      <c r="W10" s="2" t="n">
+        <v>34.1102848740697</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>254.340856720556</v>
       </c>
     </row>
     <row r="11">
@@ -7449,61 +7565,61 @@
         <v>39.56283070651072</v>
       </c>
       <c r="F11" s="2" t="n">
+        <v>24.27818587440447</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>98.6116966075774</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
+        <v>49.2544955448092</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>47.33250285039934</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>47.33250285039934</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>46.38585279339136</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>49.86108608645311</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>49.8610860864531</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>49.8610860864531</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>41.27778681628659</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="P11" s="2" t="n">
         <v>24.79345222836741</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>49.86108608645308</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="R11" s="2" t="n">
         <v>49.86108608645308</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="S11" s="2" t="n">
         <v>41.2777868162866</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="T11" s="2" t="n">
         <v>41.2777868162866</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="U11" s="2" t="n">
         <v>24.79345222836744</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="V11" s="2" t="n">
         <v>24.79345222836744</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>42.88468344234155</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>51.83930781587688</v>
-      </c>
-      <c r="W11" t="n">
-        <v>24.27818587440447</v>
-      </c>
-      <c r="X11" t="n">
-        <v>49.2544955448092</v>
+      <c r="W11" s="2" t="n">
+        <v>41.64390446764779</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>50.99219905009992</v>
       </c>
     </row>
     <row r="12">
@@ -7525,61 +7641,61 @@
         <v>30.94067580555833</v>
       </c>
       <c r="F12" s="2" t="n">
+        <v>19.61701044712016</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>88.6615481068378</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
+        <v>40.48007979745215</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>77.81175772311749</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>77.81175772311748</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>75.94427553776266</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>117.553731679799</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>117.553731679799</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>117.553731679799</v>
       </c>
       <c r="M12" s="2" t="n">
+        <v>117.553731679799</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>117.553731679799</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>38.10954179367167</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>24.77877022156451</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>117.553731679799</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="R12" s="2" t="n">
         <v>117.553731679799</v>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="S12" s="2" t="n">
         <v>38.10954179367167</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="T12" s="2" t="n">
         <v>38.10954179367167</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="U12" s="2" t="n">
         <v>24.7787702215645</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="V12" s="2" t="n">
         <v>24.7787702215645</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>40.04113192877045</v>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>130.2728115138363</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.61701044712016</v>
-      </c>
-      <c r="X12" t="n">
-        <v>40.48007979745215</v>
+      <c r="W12" s="2" t="n">
+        <v>39.66729446369943</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>124.3612134251785</v>
       </c>
     </row>
     <row r="13">
@@ -7601,61 +7717,61 @@
         <v>94.17864685117233</v>
       </c>
       <c r="F13" s="2" t="n">
+        <v>51.50764169239473</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>186.9483287457134</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
+        <v>86.24822714450288</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>292.9935734046114</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>292.9935734046113</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>286.2547212163053</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>324.4406618972106</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>324.4406618972105</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>324.4406618972105</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>245.2514018961825</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>121.200331417889</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>324.4406618972104</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="R13" s="2" t="n">
         <v>324.4406618972104</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="S13" s="2" t="n">
         <v>245.251401896183</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="T13" s="2" t="n">
         <v>245.251401896183</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="U13" s="2" t="n">
         <v>121.2003314178887</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="V13" s="2" t="n">
         <v>121.2003314178887</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>254.9540560991221</v>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>333.7708523617817</v>
-      </c>
-      <c r="W13" t="n">
-        <v>51.50764169239473</v>
-      </c>
-      <c r="X13" t="n">
-        <v>86.24822714450288</v>
+      <c r="W13" s="2" t="n">
+        <v>249.8641182762686</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>328.2413106004485</v>
       </c>
     </row>
     <row r="14">
@@ -7677,61 +7793,61 @@
         <v>35.16658028962565</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>21.9205342021058</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>139.9688809708051</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
+        <v>63.18533145172209</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>125.5029051695527</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>125.5029051695527</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>122.8673441609921</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>135.6716091572296</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>135.6716091572295</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>135.6716091572295</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>106.9624779872631</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>52.04542467740351</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>135.6716091572299</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="R14" s="2" t="n">
         <v>135.6716091572299</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="S14" s="2" t="n">
         <v>106.9624779872628</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="T14" s="2" t="n">
         <v>106.9624779872628</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="U14" s="2" t="n">
         <v>52.04542467740354</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="V14" s="2" t="n">
         <v>52.04542467740354</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>112.8441450348056</v>
-      </c>
-      <c r="V14" s="2" t="n">
-        <v>138.4479745464489</v>
-      </c>
-      <c r="W14" t="n">
-        <v>21.9205342021058</v>
-      </c>
-      <c r="X14" t="n">
-        <v>63.18533145172209</v>
+      <c r="W14" s="2" t="n">
+        <v>108.1498347722911</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>140.5830492930381</v>
       </c>
     </row>
     <row r="15">
@@ -7753,61 +7869,61 @@
         <v>6.223128848904347</v>
       </c>
       <c r="F15" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>6.223128848904347</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>10.19754055468341</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>10.19754055468341</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>9.993589743589745</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>9.458164835542291</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>9.458164835542291</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>9.458164835542291</v>
       </c>
       <c r="M15" s="2" t="n">
+        <v>9.458164835542291</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>9.458164835542291</v>
+      </c>
+      <c r="O15" s="2" t="n">
         <v>11.30212739360246</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>10.30440158605652</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>9.458164835542295</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="R15" s="2" t="n">
         <v>9.458164835542295</v>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="S15" s="2" t="n">
         <v>11.30212739360245</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="T15" s="2" t="n">
         <v>11.30212739360245</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="U15" s="2" t="n">
         <v>10.30440158605652</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="V15" s="2" t="n">
         <v>10.30440158605652</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>11.75413197094962</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>9.496174338698417</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.881896884283592</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.881896884283592</v>
+      <c r="W15" s="2" t="n">
+        <v>11.33548858150522</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>9.476715757756224</v>
       </c>
     </row>
     <row r="16">
@@ -7829,61 +7945,61 @@
         <v>188.9246547467871</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>94.20345180303136</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>772.3589140731528</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
+        <v>274.1184846161911</v>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>1003.748472342274</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>1056.007849028164</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>1032.775676349545</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>1426.864607154702</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>1426.864607154701</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>1426.864607154701</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>914.129060439588</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>345.8704013120807</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>1426.864607154705</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="R16" s="2" t="n">
         <v>1426.864607154705</v>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="S16" s="2" t="n">
         <v>914.1290604395878</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="T16" s="2" t="n">
         <v>914.1290604395878</v>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="U16" s="2" t="n">
         <v>345.870401312081</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="V16" s="2" t="n">
         <v>345.870401312081</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>967.8774022465338</v>
-      </c>
-      <c r="V16" s="2" t="n">
-        <v>1512.932250311565</v>
-      </c>
-      <c r="W16" t="n">
-        <v>94.20345180303136</v>
-      </c>
-      <c r="X16" t="n">
-        <v>274.1184846161911</v>
+      <c r="W16" s="2" t="n">
+        <v>953.8731660379115</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>1505.581654613894</v>
       </c>
     </row>
     <row r="17">
@@ -7905,61 +8021,61 @@
         <v>21.57858629762915</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>14.35176635029988</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>107.4629161326766</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
+        <v>47.93631306284109</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>123.6827696735525</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>123.6827696735525</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>121.0854315104078</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>160.7050613511514</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>160.7050613511513</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>160.7050613511513</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="O17" s="2" t="n">
         <v>86.69574979544262</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>48.55112208776874</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>160.7050613511512</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="R17" s="2" t="n">
         <v>160.7050613511512</v>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="S17" s="2" t="n">
         <v>86.69574979544259</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="T17" s="2" t="n">
         <v>86.69574979544259</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="U17" s="2" t="n">
         <v>48.55112208776875</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="V17" s="2" t="n">
         <v>48.55112208776875</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>90.59454197909548</v>
-      </c>
-      <c r="V17" s="2" t="n">
-        <v>174.3038165894203</v>
-      </c>
-      <c r="W17" t="n">
-        <v>14.35176635029988</v>
-      </c>
-      <c r="X17" t="n">
-        <v>47.93631306284109</v>
+      <c r="W17" s="2" t="n">
+        <v>87.80902547171854</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>170.4358031713677</v>
       </c>
     </row>
     <row r="18">
@@ -7978,64 +8094,64 @@
         <v>153.5063191216989</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>54.42563084569721</v>
+        <v>54.42563084569726</v>
       </c>
       <c r="F18" s="2" t="n">
+        <v>32.01412407426785</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>236.6828022651465</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
+        <v>100.6878204145854</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>159.0613711885023</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>159.0613711885023</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>156.0392051359208</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>198.2082231056915</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>198.2082231056914</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>198.2082231056914</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>116.373231289557</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>56.49052560682633</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>198.2082231056916</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="R18" s="2" t="n">
         <v>198.2082231056916</v>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="S18" s="2" t="n">
         <v>116.3732312895566</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="T18" s="2" t="n">
         <v>116.3732312895566</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="U18" s="2" t="n">
         <v>56.49052560682637</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="V18" s="2" t="n">
         <v>56.49052560682637</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>123.7092022756005</v>
-      </c>
-      <c r="V18" s="2" t="n">
-        <v>211.8709226329803</v>
-      </c>
-      <c r="W18" t="n">
-        <v>32.01412407426783</v>
-      </c>
-      <c r="X18" t="n">
-        <v>100.6878204145854</v>
+      <c r="W18" s="2" t="n">
+        <v>116.1399239726856</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>208.3211052502791</v>
       </c>
     </row>
     <row r="19">
@@ -8057,61 +8173,61 @@
         <v>262.4070949788439</v>
       </c>
       <c r="F19" s="2" t="n">
+        <v>125.2590957378396</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>672.1889581826362</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
+        <v>249.9812478195048</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>421.7498448185209</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>575.6382317549858</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>564.125467119886</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>1114.691652144382</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1114.691652144382</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>1114.691652144382</v>
       </c>
       <c r="M19" s="2" t="n">
+        <v>1114.691652144382</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1114.691652144382</v>
+      </c>
+      <c r="O19" s="2" t="n">
         <v>635.9376562683256</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>217.2386746189102</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>1114.691652144385</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="R19" s="2" t="n">
         <v>1114.691652144385</v>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>635.9376562683261</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="T19" s="2" t="n">
         <v>635.9376562683261</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="U19" s="2" t="n">
         <v>217.2386746189103</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="V19" s="2" t="n">
         <v>217.2386746189103</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>669.7421522924902</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>1212.57805917571</v>
-      </c>
-      <c r="W19" t="n">
-        <v>125.2590957378396</v>
-      </c>
-      <c r="X19" t="n">
-        <v>249.9812478195048</v>
+      <c r="W19" s="2" t="n">
+        <v>670.5654263315668</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>1209.82486843931</v>
       </c>
     </row>
     <row r="20">
@@ -8133,61 +8249,61 @@
         <v>288.507746425553</v>
       </c>
       <c r="F20" s="2" t="n">
+        <v>135.9951668482977</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>1782.49431863192</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
+        <v>530.8757765188035</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>1013.570171471442</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>1067.730871536711</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>1046.376254105977</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1918.226528674924</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1918.226528674924</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1918.226528674924</v>
       </c>
       <c r="M20" s="2" t="n">
+        <v>1918.226528674924</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1918.226528674924</v>
+      </c>
+      <c r="O20" s="2" t="n">
         <v>1111.682877581138</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>334.6245073550722</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>1918.226528674925</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="R20" s="2" t="n">
         <v>1918.226528674925</v>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="S20" s="2" t="n">
         <v>1111.682877581138</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="T20" s="2" t="n">
         <v>1111.682877581138</v>
       </c>
-      <c r="S20" s="2" t="n">
+      <c r="U20" s="2" t="n">
         <v>334.624507355072</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="V20" s="2" t="n">
         <v>334.624507355072</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>1212.403983721935</v>
-      </c>
-      <c r="V20" s="2" t="n">
-        <v>2057.246558511828</v>
-      </c>
-      <c r="W20" t="n">
-        <v>135.9951668482977</v>
-      </c>
-      <c r="X20" t="n">
-        <v>530.8757765188035</v>
+      <c r="W20" s="2" t="n">
+        <v>1177.252795758544</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>2066.176882794377</v>
       </c>
     </row>
     <row r="21">
@@ -8209,61 +8325,61 @@
         <v>288.5103905458261</v>
       </c>
       <c r="F21" s="2" t="n">
+        <v>135.996247738189</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>1152.508392338651</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
+        <v>384.9639588136019</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>1331.752693342869</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>1334.2572945693</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>1300.900862205068</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>2933.853361777305</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>2933.853361777304</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>2933.853361777304</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>1771.038679713454</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>582.8715320516791</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>2933.853361777306</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>2933.853361777306</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="S21" s="2" t="n">
         <v>1771.038679713452</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="T21" s="2" t="n">
         <v>1771.038679713452</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="U21" s="2" t="n">
         <v>582.8715320516792</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="V21" s="2" t="n">
         <v>582.8715320516792</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>1875.159902155221</v>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>3182.729383356123</v>
-      </c>
-      <c r="W21" t="n">
-        <v>135.996247738189</v>
-      </c>
-      <c r="X21" t="n">
-        <v>384.9639588136019</v>
+      <c r="W21" s="2" t="n">
+        <v>1926.989095139347</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>3204.045693303023</v>
       </c>
     </row>
     <row r="22">
@@ -8282,64 +8398,64 @@
         <v>1377.951482341825</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>310.8703778357537</v>
+        <v>310.8703778357543</v>
       </c>
       <c r="F22" s="2" t="n">
+        <v>145.0910757257476</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>1019.11674600522</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
+        <v>354.0160885041838</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>804.6273553053973</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>818.1011108998474</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>575.1250809625926</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>970.7828260845469</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="M22" s="2" t="n">
         <v>970.7828260845463</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>970.7828260845463</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>487.0569072979667</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>182.8633148377885</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>970.7828260845465</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="R22" s="2" t="n">
         <v>970.7828260845465</v>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="S22" s="2" t="n">
         <v>487.0569072979672</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="T22" s="2" t="n">
         <v>487.0569072979672</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="U22" s="2" t="n">
         <v>182.8633148377886</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="V22" s="2" t="n">
         <v>182.8633148377886</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>515.9272814041871</v>
-      </c>
-      <c r="V22" s="2" t="n">
-        <v>1005.016369881499</v>
-      </c>
-      <c r="W22" t="n">
-        <v>145.0910757257474</v>
-      </c>
-      <c r="X22" t="n">
-        <v>354.0160885041838</v>
+      <c r="W22" s="2" t="n">
+        <v>500.6265281280895</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>1006.613772155264</v>
       </c>
     </row>
     <row r="23">
@@ -8361,61 +8477,61 @@
         <v>275.3006232985392</v>
       </c>
       <c r="F23" s="2" t="n">
+        <v>130.5795261988503</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>2443.4114085821</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
+        <v>655.0984682910046</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>848.8851915781844</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>883.2611115348235</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="K23" s="2" t="n">
         <v>865.595889304127</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>1961.116323246852</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>1961.116323246852</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>1961.116323246852</v>
       </c>
       <c r="M23" s="2" t="n">
+        <v>1961.116323246852</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1961.116323246852</v>
+      </c>
+      <c r="O23" s="2" t="n">
         <v>1097.797369118902</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>300.8034198641895</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>1961.11632324685</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="R23" s="2" t="n">
         <v>1961.11632324685</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="S23" s="2" t="n">
         <v>1097.797369118906</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="T23" s="2" t="n">
         <v>1097.797369118906</v>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="U23" s="2" t="n">
         <v>300.8034198641898</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="V23" s="2" t="n">
         <v>300.8034198641898</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>1217.954800512522</v>
-      </c>
-      <c r="V23" s="2" t="n">
-        <v>2161.079708508654</v>
-      </c>
-      <c r="W23" t="n">
-        <v>130.5795261988503</v>
-      </c>
-      <c r="X23" t="n">
-        <v>655.0984682910046</v>
+      <c r="W23" s="2" t="n">
+        <v>1185.911313165701</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>2124.01878375962</v>
       </c>
     </row>
     <row r="24">
@@ -8437,61 +8553,61 @@
         <v>111.320330100519</v>
       </c>
       <c r="F24" s="2" t="n">
+        <v>59.54587886365636</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>691.0777210943435</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
+        <v>236.0536915685313</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>2128.450324204537</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>2171.723686015249</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>1300.862487923134</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>3126.18566880461</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>3126.18566880461</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>3126.18566880461</v>
       </c>
       <c r="M24" s="2" t="n">
+        <v>3126.18566880461</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>3126.18566880461</v>
+      </c>
+      <c r="O24" s="2" t="n">
         <v>887.6343072748797</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>357.5420041753196</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>3126.185668804606</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="R24" s="2" t="n">
         <v>3126.185668804606</v>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="S24" s="2" t="n">
         <v>887.6343072748805</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="T24" s="2" t="n">
         <v>887.6343072748805</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="U24" s="2" t="n">
         <v>357.5420041753196</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="V24" s="2" t="n">
         <v>357.5420041753196</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>937.0141323326557</v>
-      </c>
-      <c r="V24" s="2" t="n">
-        <v>3360.569290714359</v>
-      </c>
-      <c r="W24" t="n">
-        <v>59.54587886365636</v>
-      </c>
-      <c r="X24" t="n">
-        <v>236.0536915685313</v>
+      <c r="W24" s="2" t="n">
+        <v>916.7585913209008</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>3351.353169810148</v>
       </c>
     </row>
     <row r="25">
@@ -8513,61 +8629,61 @@
         <v>509.8254375061286</v>
       </c>
       <c r="F25" s="2" t="n">
+        <v>222.8221513847066</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>5573.824861515769</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
+        <v>1308.685036527036</v>
+      </c>
+      <c r="I25" s="2" t="n">
         <v>1955.186859493807</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>2007.418174584036</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>1423.259485780082</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>3930.042293288787</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>3930.042293288787</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>3930.042293288787</v>
       </c>
       <c r="M25" s="2" t="n">
+        <v>3930.042293288787</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>3930.042293288787</v>
+      </c>
+      <c r="O25" s="2" t="n">
         <v>1585.345045082565</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>411.2685218988508</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>3930.042293288785</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="R25" s="2" t="n">
         <v>3930.042293288785</v>
       </c>
-      <c r="Q25" s="2" t="n">
+      <c r="S25" s="2" t="n">
         <v>1585.345045082566</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="T25" s="2" t="n">
         <v>1585.345045082566</v>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="U25" s="2" t="n">
         <v>411.2685218988514</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="V25" s="2" t="n">
         <v>411.2685218988514</v>
       </c>
-      <c r="U25" s="2" t="n">
-        <v>1727.014599662814</v>
-      </c>
-      <c r="V25" s="2" t="n">
-        <v>4280.685882503204</v>
-      </c>
-      <c r="W25" t="n">
-        <v>222.8221513847066</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1308.685036527036</v>
+      <c r="W25" s="2" t="n">
+        <v>1706.163340653995</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>4274.319993004987</v>
       </c>
     </row>
     <row r="26">
@@ -8589,61 +8705,61 @@
         <v>261.195153950476</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>124.757235171582</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>1335.321685246217</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
+        <v>418.7723011987895</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>255333.6498407797</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>269612.5273851222</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="K26" s="2" t="n">
         <v>13750.23889664124</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>493549.2649017496</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>493549.2649017496</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>493549.2649017496</v>
       </c>
       <c r="M26" s="2" t="n">
+        <v>493549.2649017496</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>493549.2649017496</v>
+      </c>
+      <c r="O26" s="2" t="n">
         <v>14395.8984571961</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>4511.0569155873</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>493549.2649017493</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="R26" s="2" t="n">
         <v>493549.2649017493</v>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="S26" s="2" t="n">
         <v>14395.89845719607</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="T26" s="2" t="n">
         <v>14395.89845719607</v>
       </c>
-      <c r="S26" s="2" t="n">
+      <c r="U26" s="2" t="n">
         <v>4511.056915587296</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="V26" s="2" t="n">
         <v>4511.056915587296</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>14978.82322944805</v>
-      </c>
-      <c r="V26" s="2" t="n">
-        <v>533729.0919429567</v>
-      </c>
-      <c r="W26" t="n">
-        <v>124.757235171582</v>
-      </c>
-      <c r="X26" t="n">
-        <v>418.7723011987895</v>
+      <c r="W26" s="2" t="n">
+        <v>15498.8073599569</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>541558.1880342518</v>
       </c>
     </row>
   </sheetData>
@@ -9020,7 +9136,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9062,17 +9178,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="M2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.107820959730019e-16</v>
+        <v>0.05354545454545458</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1.807191134537733e-16</v>
+        <v>0.006738102501525392</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -9115,6 +9231,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.5160159405139225</v>
       </c>
@@ -9172,16 +9289,16 @@
         </is>
       </c>
       <c r="AV2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW2" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>4094.999999999999</v>
+        <v>4086.603466515866</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>2.220988282717773e-16</v>
+        <v>0.002050435527260969</v>
       </c>
       <c r="AZ2" s="2" t="n">
         <v>2087.786392570886</v>
@@ -9202,7 +9319,7 @@
         <v>0.4710057884723031</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -9240,6 +9357,7 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Arabian_Sea_off_Karnataka (2000)</t>
@@ -9250,17 +9368,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="M3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.107820959730019e-16</v>
+        <v>0.05354545454545458</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1.807191134537733e-16</v>
+        <v>0.006738102501525392</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -9303,6 +9421,7 @@
           <t>WARN</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -9356,20 +9475,20 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="AV3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW3" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>4094.999999999997</v>
+        <v>3938.789038996875</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>7.773458989512207e-16</v>
+        <v>0.03814675482371801</v>
       </c>
       <c r="AZ3" s="2" t="n">
         <v>3649.013190011103</v>
@@ -9390,7 +9509,7 @@
         <v>0.8100120434964353</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -9401,7 +9520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9443,17 +9562,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="M4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.107820959730019e-16</v>
+        <v>0.05354545454545458</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.807191134537733e-16</v>
+        <v>0.006738102501525392</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
@@ -9496,6 +9615,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.535114568397998</v>
       </c>
@@ -9553,16 +9673,16 @@
         </is>
       </c>
       <c r="AV4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>4094.999999999998</v>
+        <v>4089.573960447514</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>5.552470706794434e-16</v>
+        <v>0.0013250401837573</v>
       </c>
       <c r="AZ4" s="2" t="n">
         <v>763.9785984567641</v>
@@ -9583,7 +9703,7 @@
         <v>0.1562867159466777</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9658,12 +9778,14 @@
       <c r="C2" s="2" t="n">
         <v>698.6957964207286</v>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.170621684107626</v>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9677,12 +9799,14 @@
       <c r="C3" s="2" t="n">
         <v>2189.941127281998</v>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.534784158066422</v>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9691,485 +9815,489 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>568.4879724997598</v>
+        <v>568.48797249976</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>568.4879724997598</v>
-      </c>
+        <v>568.48797249976</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.1388249017093431</v>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ulanowicz_globalTEmean</t>
+          <t>SPPR_1995_TEmean_catch</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2654.250271352967</v>
+        <v>291.4556411587741</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2654.250271352967</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>2446.609691466923</v>
-      </c>
+        <v>291.4556411587741</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6481685644329589</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.5974626841189067</v>
-      </c>
+        <v>0.07117353874451138</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Ulanowicz_TE</t>
+          <t>Ulanowicz_globalTEmean</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2076.538867997283</v>
+        <v>2654.250271352967</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2076.538867997283</v>
+        <v>2654.250271352967</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1818.550159244158</v>
+        <v>2446.609691466923</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.5070912986562351</v>
+        <v>0.6481685644329589</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.4440903929778163</v>
+        <v>0.5974626841189067</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EwE_TE_noEE</t>
+          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2169.18523201408</v>
+        <v>893.3240333517341</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2169.18523201408</v>
+        <v>893.3240333517341</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1902.54903915625</v>
+        <v>803.1575703666068</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5297155633734016</v>
+        <v>0.2181499470944405</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.4646029399648961</v>
+        <v>0.1961312748148002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EwE_TE_EE</t>
+          <t>Ulanowicz_TE</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2073.345115856347</v>
+        <v>2076.538867997283</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2073.345115856347</v>
+        <v>2076.538867997283</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1817.592651444137</v>
+        <v>1818.550159244158</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5063113836035035</v>
+        <v>0.5070912986562351</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4438565693392275</v>
+        <v>0.4440903929778163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SPPR_2015</t>
+          <t>EwE_TE_noEE</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3649.013190011104</v>
+        <v>2169.18523201408</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3649.013190011103</v>
+        <v>2169.18523201408</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3649.013190011104</v>
+        <v>1902.54903915625</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8910899120906235</v>
+        <v>0.5297155633734016</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.8910899120906236</v>
+        <v>0.4646029399648961</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>new_TE_noEEfix</t>
+          <t>EwE_TE_EE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3649.013190011103</v>
+        <v>2073.345115856347</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3649.013190011103</v>
+        <v>2073.345115856347</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3316.999318117902</v>
+        <v>1817.592651444137</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8910899120906234</v>
+        <v>0.5063113836035035</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8100120434964353</v>
+        <v>0.4438565693392275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>new_TE_EEfix</t>
+          <t>SPPR_2015</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3649.013190011103</v>
+        <v>3649.013190011104</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>3649.013190011103</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3316.999318117902</v>
+        <v>3649.013190011104</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.8910899120906234</v>
+        <v>0.8910899120906235</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.8100120434964353</v>
+        <v>0.8910899120906236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>new_GE</t>
+          <t>new_TE_noEEfix</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2087.786392570886</v>
+        <v>3649.013190011103</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2087.786392570886</v>
+        <v>3649.013190011103</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1928.768703794081</v>
+        <v>3316.999318117902</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.5098379469037572</v>
+        <v>0.8910899120906234</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.4710057884723031</v>
+        <v>0.8100120434964353</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>new_WithEgestion</t>
+          <t>new_TE_EEfix</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>763.9785984567641</v>
+        <v>3649.013190011103</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>763.9785984567641</v>
+        <v>3649.013190011103</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>639.9941018016452</v>
+        <v>3316.999318117902</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1865637603069021</v>
+        <v>0.8910899120906234</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.1562867159466777</v>
+        <v>0.8100120434964353</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>sym_TE_asPP</t>
+          <t>new_GE</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3649.013190011107</v>
+        <v>2087.786392570886</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3649.013190011107</v>
+        <v>2087.786392570886</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3316.999318117906</v>
+        <v>1928.768703794081</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8910899120906244</v>
+        <v>0.5098379469037572</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.8100120434964362</v>
+        <v>0.4710057884723031</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>sym_TE_asDC</t>
+          <t>new_WithEgestion</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3649.013190011107</v>
+        <v>763.9785984567641</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3649.013190011107</v>
+        <v>763.9785984567641</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3316.999318117906</v>
+        <v>639.9941018016452</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.8910899120906244</v>
+        <v>0.1865637603069021</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8100120434964362</v>
+        <v>0.1562867159466777</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>sym_GE_asPP</t>
+          <t>sym_TE_asPP</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2087.786392570886</v>
+        <v>3649.013190011107</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2087.786392570886</v>
+        <v>3649.013190011107</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1928.768703794081</v>
+        <v>3316.999318117906</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.5098379469037572</v>
+        <v>0.8910899120906244</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.4710057884723031</v>
+        <v>0.8100120434964362</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>sym_GE_asDC</t>
+          <t>sym_TE_asDC</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2087.786392570886</v>
+        <v>3649.013190011107</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2087.786392570886</v>
+        <v>3649.013190011107</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1928.768703794081</v>
+        <v>3316.999318117906</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.5098379469037572</v>
+        <v>0.8910899120906244</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.4710057884723031</v>
+        <v>0.8100120434964362</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>sym_WithEgestion_asPP</t>
+          <t>sym_GE_asPP</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>763.9785984567642</v>
+        <v>2087.786392570886</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>763.9785984567642</v>
+        <v>2087.786392570886</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>639.9941018016455</v>
+        <v>1928.768703794081</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.1865637603069021</v>
+        <v>0.5098379469037572</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.1562867159466778</v>
+        <v>0.4710057884723031</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>sym_WithEgestion_asDC</t>
+          <t>sym_GE_asDC</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>763.9785984567642</v>
+        <v>2087.786392570886</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>763.9785984567642</v>
+        <v>2087.786392570886</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>639.9941018016455</v>
+        <v>1928.768703794081</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.1865637603069021</v>
+        <v>0.5098379469037572</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.1562867159466778</v>
+        <v>0.4710057884723031</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MC_new_GE</t>
+          <t>sym_WithEgestion_asPP</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2229.761685609361</v>
+        <v>763.9785984567642</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2229.761685609361</v>
+        <v>763.9785984567642</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2058.091036674575</v>
+        <v>639.9941018016455</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.5445083481341541</v>
+        <v>0.1865637603069021</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.502586333742265</v>
+        <v>0.1562867159466778</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>MC_new_TE_EEfix</t>
+          <t>sym_WithEgestion_asDC</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3928.003229400456</v>
+        <v>763.9785984567642</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3928.003229400456</v>
+        <v>763.9785984567642</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3545.2588432009</v>
+        <v>639.9941018016455</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.9592193478389391</v>
+        <v>0.1865637603069021</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.865753075262735</v>
+        <v>0.1562867159466778</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SPPR_1995_TEmean_catch</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>291.455641158774</v>
-      </c>
-      <c r="C22" t="n">
-        <v>291.455641158774</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MC_new_GE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2205.71200238859</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>2205.71200238859</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2030.30761385936</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>4095</v>
       </c>
-      <c r="F22" t="n">
-        <v>0.07117353874451136</v>
+      <c r="F22" s="2" t="n">
+        <v>0.5386354096187032</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0.4958016151060708</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Ulanowicz_globalTEmean_catch</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>893.3240333517341</v>
-      </c>
-      <c r="C23" t="n">
-        <v>893.3240333517341</v>
-      </c>
-      <c r="D23" t="n">
-        <v>803.1575703666068</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>MC_new_TE_EEfix</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>3916.023132826604</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>3916.023132826604</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>3540.0733452303</v>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>4095</v>
       </c>
-      <c r="F23" t="n">
-        <v>0.2181499470944405</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.1961312748148002</v>
+      <c r="F23" s="2" t="n">
+        <v>0.9562938053300619</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0.8644867753920146</v>
       </c>
     </row>
   </sheetData>
@@ -10341,6 +10469,7 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -10353,6 +10482,7 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -10365,6 +10495,7 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -10377,6 +10508,7 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -10389,6 +10521,7 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -10401,6 +10534,7 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -10413,6 +10547,7 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -10425,6 +10560,7 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -10437,6 +10573,7 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -10492,12 +10629,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>method: Ulanowicz_globalTEmean</t>
+          <t>method: SPPR_1995_TEmean_catch</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10509,12 +10646,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>method: Ulanowicz_TE</t>
+          <t>method: Ulanowicz_globalTEmean</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, per-group TE (Jensen-able on TE).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10526,12 +10663,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>method: EwE_TE_noEE</t>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EwE path enumeration without EE weighting -- heavy method.</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10543,12 +10680,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>method: EwE_TE_EE</t>
+          <t>method: Ulanowicz_TE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EwE path enumeration with EE weighting -- heavy method.</t>
+          <t>Nullspace form of the EwE path sum, per-group TE (Jensen-able on TE).</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10560,12 +10697,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>method: SPPR_2015</t>
+          <t>method: EwE_TE_noEE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2015 Leontief method, includes cycles. Takes no arguments: PP-only filtering is applied downstream via get_PPR.</t>
+          <t>EwE path enumeration without EE weighting -- heavy method.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10577,12 +10714,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>method: new_TE_noEEfix</t>
+          <t>method: EwE_TE_EE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Primary solver, TE_option='TE', EE=0 groups left unrepaired (reproduces 2015).</t>
+          <t>EwE path enumeration with EE weighting -- heavy method.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10594,12 +10731,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>method: new_TE_EEfix</t>
+          <t>method: SPPR_2015</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Primary solver, TE_option='TE', EE=0 groups repaired.</t>
+          <t>2015 Leontief method, includes cycles. Takes no arguments: PP-only filtering is applied downstream via get_PPR.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10611,12 +10748,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>method: new_GE</t>
+          <t>method: new_TE_noEEfix</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Primary solver, TE_option='GE' (should sit below TE).</t>
+          <t>Primary solver, TE_option='TE', EE=0 groups left unrepaired (reproduces 2015).</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10628,12 +10765,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>method: new_WithEgestion</t>
+          <t>method: new_TE_EEfix</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Primary solver, TE_option='With Egestion' (should sit below GE).</t>
+          <t>Primary solver, TE_option='TE', EE=0 groups repaired.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10645,12 +10782,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>method: sym_TE_asPP</t>
+          <t>method: new_GE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Symbolic solver, TE_option='TE', diet_import_option='as_PP'.</t>
+          <t>Primary solver, TE_option='GE' (should sit below TE).</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -10662,12 +10799,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>method: sym_TE_asDC</t>
+          <t>method: new_WithEgestion</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Symbolic solver, TE_option='TE', diet_import_option='as_DC'.</t>
+          <t>Primary solver, TE_option='With Egestion' (should sit below GE).</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10679,12 +10816,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>method: sym_GE_asPP</t>
+          <t>method: sym_TE_asPP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Symbolic solver, TE_option='GE', diet_import_option='as_PP'.</t>
+          <t>Symbolic solver, TE_option='TE', diet_import_option='as_PP'.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10696,12 +10833,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>method: sym_GE_asDC</t>
+          <t>method: sym_TE_asDC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Symbolic solver, TE_option='GE', diet_import_option='as_DC'.</t>
+          <t>Symbolic solver, TE_option='TE', diet_import_option='as_DC'.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -10713,12 +10850,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>method: sym_WithEgestion_asPP</t>
+          <t>method: sym_GE_asPP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Symbolic solver, TE_option='With Egestion', diet_import_option='as_PP'.</t>
+          <t>Symbolic solver, TE_option='GE', diet_import_option='as_PP'.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10730,12 +10867,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>method: sym_WithEgestion_asDC</t>
+          <t>method: sym_GE_asDC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Symbolic solver, TE_option='With Egestion', diet_import_option='as_DC'.</t>
+          <t>Symbolic solver, TE_option='GE', diet_import_option='as_DC'.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10747,12 +10884,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>method: MC_new_GE</t>
+          <t>method: sym_WithEgestion_asPP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Monte-Carlo over TE (10%/20%), kind='new', TE_option='GE', diverged draws excluded.</t>
+          <t>Symbolic solver, TE_option='With Egestion', diet_import_option='as_PP'.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10764,46 +10901,46 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
+          <t>method: sym_WithEgestion_asDC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Symbolic solver, TE_option='With Egestion', diet_import_option='as_DC'.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>method: MC_new_GE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Monte-Carlo over TE (10%/20%), kind='new', TE_option='GE', diverged draws excluded.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>method: MC_new_TE_EEfix</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Monte-Carlo over TE (10%/20%), kind='new', TE_option='TE' with fix_EE_0_cases=True, diverged draws excluded.</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>method: SPPR_1995_TEmean_catch</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>method: Ulanowicz_globalTEmean_catch</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
